--- a/docs/d/20/inyear.xlsx
+++ b/docs/d/20/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6716,8 +6716,8 @@
       <c r="V59" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W59" s="9" t="n">
-        <v>2</v>
+      <c r="W59" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X59" s="10" t="n">
         <v>5</v>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Alqimmah</t>
+          <t>ALQIMMAH</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
@@ -10959,7 +10959,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10973,13 +10973,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
@@ -11020,8 +11020,8 @@
       <c r="V101" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W101" s="9" t="n">
-        <v>3</v>
+      <c r="W101" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X101" s="10" t="n">
         <v>7</v>
@@ -13623,7 +13623,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>

--- a/docs/d/20/inyear.xlsx
+++ b/docs/d/20/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,11 @@
       <c r="AB3" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -1840,7 +1844,11 @@
       <c r="AB11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC11" s="4" t="inlineStr"/>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2046,7 +2054,11 @@
       <c r="AB13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC13" s="4" t="inlineStr"/>
+      <c r="AC13" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -3068,7 +3080,11 @@
       <c r="AB23" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC23" s="4" t="inlineStr"/>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -4286,7 +4302,11 @@
       <c r="AB35" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC35" s="4" t="inlineStr"/>
+      <c r="AC35" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -5102,7 +5122,11 @@
       <c r="AB43" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC43" s="4" t="inlineStr"/>
+      <c r="AC43" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -6734,7 +6758,11 @@
       <c r="AB59" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC59" s="4" t="inlineStr"/>
+      <c r="AC59" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -6936,7 +6964,11 @@
       <c r="AB61" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC61" s="4" t="inlineStr"/>
+      <c r="AC61" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -7142,7 +7174,11 @@
       <c r="AB63" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC63" s="4" t="inlineStr"/>
+      <c r="AC63" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -7453,7 +7489,11 @@
       <c r="AB66" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC66" s="4" t="inlineStr"/>
+      <c r="AC66" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -8483,7 +8523,11 @@
       <c r="AB76" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC76" s="4" t="inlineStr"/>
+      <c r="AC76" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -10018,7 +10062,11 @@
       <c r="AB91" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC91" s="4" t="inlineStr"/>
+      <c r="AC91" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -10119,7 +10167,11 @@
       <c r="AB92" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC92" s="4" t="inlineStr"/>
+      <c r="AC92" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -10321,7 +10373,11 @@
       <c r="AB94" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC94" s="4" t="inlineStr"/>
+      <c r="AC94" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -11240,7 +11296,11 @@
       <c r="AB103" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC103" s="4" t="inlineStr"/>
+      <c r="AC103" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -11749,7 +11809,11 @@
       <c r="AB108" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC108" s="4" t="inlineStr"/>
+      <c r="AC108" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">

--- a/docs/d/20/inyear.xlsx
+++ b/docs/d/20/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 14 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 14 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 51 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 50 clubs short</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="P4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="9" t="n">
         <v>0</v>
@@ -3454,16 +3454,16 @@
         </is>
       </c>
       <c r="P27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" s="9" t="n">
         <v>0</v>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8102,8 +8102,8 @@
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="9" t="n">
-        <v>0</v>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9626,8 +9626,8 @@
       <c r="T87" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U87" s="9" t="n">
-        <v>0</v>
+      <c r="U87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V87" s="9" t="n">
         <v>0</v>
@@ -10135,7 +10135,7 @@
         <v>2</v>
       </c>
       <c r="R92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S92" s="10" t="n">
         <v>2</v>
@@ -12076,7 +12076,7 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q111" s="9" t="n">
         <v>0</v>
@@ -13786,7 +13786,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13885,7 +13885,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>

--- a/docs/d/20/inyear.xlsx
+++ b/docs/d/20/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 14 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 14 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 50 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 36 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -918,8 +918,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -1007,11 +1007,11 @@
       <c r="U3" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V3" s="9" t="n">
-        <v>0</v>
+      <c r="V3" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W3" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X3" s="10" t="n">
         <v>7</v>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1124,8 +1124,8 @@
       <c r="Y4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" s="9" t="n">
-        <v>0</v>
+      <c r="Z4" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA4" s="10" t="n">
         <v>1</v>
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1633,8 +1633,8 @@
       <c r="Y9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="9" t="n">
-        <v>0</v>
+      <c r="Z9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA9" s="10" t="n">
         <v>1</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2952,11 +2952,11 @@
       <c r="S22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" s="9" t="n">
-        <v>0</v>
+      <c r="T22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V22" s="9" t="n">
         <v>1</v>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="P28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="9" t="n">
         <v>0</v>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -5012,8 +5012,8 @@
       <c r="Y42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="9" t="n">
-        <v>0</v>
+      <c r="Z42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA42" s="10" t="n">
         <v>1</v>
@@ -5451,7 +5451,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5521,8 +5521,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6626,8 +6626,8 @@
       <c r="S58" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T58" s="9" t="n">
-        <v>0</v>
+      <c r="T58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U58" s="9" t="n">
         <v>0</v>
@@ -6679,7 +6679,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6731,8 +6731,8 @@
       <c r="S59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T59" s="9" t="n">
-        <v>0</v>
+      <c r="T59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U59" s="9" t="n">
         <v>0</v>
@@ -7109,13 +7109,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>4</v>
       </c>
       <c r="W63" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X63" s="10" t="n">
         <v>5</v>
@@ -7871,7 +7871,7 @@
         </is>
       </c>
       <c r="P70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q70" s="9" t="n">
         <v>0</v>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8072,8 +8072,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P72" s="9" t="n">
-        <v>3</v>
+      <c r="P72" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q72" s="9" t="n">
         <v>0</v>
@@ -8387,7 +8387,7 @@
         <v>1</v>
       </c>
       <c r="Q75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" s="9" t="n">
         <v>0</v>
@@ -9159,7 +9159,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -9229,8 +9229,8 @@
       <c r="Y83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z83" s="9" t="n">
-        <v>0</v>
+      <c r="Z83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA83" s="10" t="n">
         <v>1</v>
@@ -9466,7 +9466,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9536,8 +9536,8 @@
       <c r="Y86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="9" t="n">
-        <v>0</v>
+      <c r="Z86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA86" s="10" t="n">
         <v>1</v>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9641,8 +9641,8 @@
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="9" t="n">
-        <v>0</v>
+      <c r="Z87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA87" s="10" t="n">
         <v>1</v>
@@ -10088,7 +10088,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10129,13 +10129,13 @@
         </is>
       </c>
       <c r="P92" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q92" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R92" s="9" t="n">
-        <v>1</v>
+      <c r="R92" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S92" s="10" t="n">
         <v>2</v>
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>4</v>
       </c>
       <c r="W93" s="10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="X93" s="10" t="n">
         <v>7</v>
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10965,8 +10965,8 @@
       <c r="T100" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U100" s="9" t="n">
-        <v>0</v>
+      <c r="U100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V100" s="10" t="n">
         <v>4</v>
@@ -11116,7 +11116,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -11186,8 +11186,8 @@
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="9" t="n">
-        <v>0</v>
+      <c r="Z102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -11366,7 +11366,7 @@
         <v>1</v>
       </c>
       <c r="Q104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R104" s="9" t="n">
         <v>0</v>
@@ -11673,7 +11673,7 @@
         <v>1</v>
       </c>
       <c r="Q107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R107" s="9" t="n">
         <v>0</v>
@@ -11744,13 +11744,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>4</v>
       </c>
       <c r="W108" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>7</v>
@@ -11936,7 +11936,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -12006,8 +12006,8 @@
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="9" t="n">
-        <v>0</v>
+      <c r="Z110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA110" s="10" t="n">
         <v>1</v>
@@ -12134,7 +12134,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12204,8 +12204,8 @@
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12303,8 +12303,8 @@
       <c r="Y113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z113" s="9" t="n">
-        <v>0</v>
+      <c r="Z113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA113" s="10" t="n">
         <v>1</v>
@@ -12827,7 +12827,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12868,7 +12868,7 @@
         </is>
       </c>
       <c r="P119" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q119" s="9" t="n">
         <v>0</v>
@@ -12897,8 +12897,8 @@
       <c r="Y119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z119" s="9" t="n">
-        <v>0</v>
+      <c r="Z119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA119" s="10" t="n">
         <v>1</v>
@@ -13124,7 +13124,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13194,8 +13194,8 @@
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="9" t="n">
-        <v>0</v>
+      <c r="Z122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA122" s="10" t="n">
         <v>1</v>
@@ -13291,7 +13291,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -13324,7 +13324,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -13423,7 +13423,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -13555,7 +13555,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -13588,7 +13588,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -13654,7 +13654,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13687,7 +13687,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13786,7 +13786,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13852,7 +13852,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -13885,7 +13885,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
@@ -13984,13 +13984,13 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -14017,7 +14017,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14083,7 +14083,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>

--- a/docs/d/20/inyear.xlsx
+++ b/docs/d/20/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 14 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 14 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 36 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 35 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1577,13 +1577,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1779,13 +1779,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
@@ -1814,8 +1814,8 @@
       <c r="R11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S11" s="9" t="n">
-        <v>1</v>
+      <c r="S11" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T11" s="10" t="n">
         <v>1</v>
@@ -1823,11 +1823,11 @@
       <c r="U11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V11" s="9" t="n">
-        <v>0</v>
+      <c r="V11" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" s="10" t="n">
         <v>7</v>
@@ -1884,17 +1884,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M12" s="8" t="n">
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="P13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" s="9" t="n">
         <v>0</v>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2401,13 +2401,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-7</v>
+        <v>-16</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2506,17 +2506,17 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-23</v>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M18" s="8" t="n">
@@ -2611,13 +2611,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2712,13 +2712,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2914,13 +2914,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -3015,13 +3015,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
@@ -3221,13 +3221,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -3326,13 +3326,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3427,13 +3427,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="P27" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q27" s="9" t="n">
         <v>1</v>
@@ -3528,13 +3528,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3730,13 +3730,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="P30" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q30" s="9" t="n">
         <v>1</v>
@@ -3775,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>0</v>
@@ -3835,13 +3835,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4037,13 +4037,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
@@ -4093,8 +4093,8 @@
       <c r="Y33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="9" t="n">
-        <v>0</v>
+      <c r="Z33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA33" s="10" t="n">
         <v>1</v>
@@ -4136,13 +4136,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>4</v>
       </c>
       <c r="W34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" s="10" t="n">
         <v>7</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4237,17 +4237,17 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M35" s="8" t="n">
@@ -4281,8 +4281,8 @@
       <c r="U35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V35" s="9" t="n">
-        <v>3</v>
+      <c r="V35" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -4631,7 +4631,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4645,13 +4645,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4692,8 +4692,8 @@
       <c r="V39" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W39" s="9" t="n">
-        <v>2</v>
+      <c r="W39" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X39" s="10" t="n">
         <v>6</v>
@@ -4750,13 +4750,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4851,17 +4851,17 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M41" s="8" t="n">
@@ -4895,11 +4895,11 @@
       <c r="U41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V41" s="9" t="n">
-        <v>1</v>
+      <c r="V41" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" s="10" t="n">
         <v>7</v>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4956,13 +4956,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -5000,14 +5000,14 @@
       <c r="U42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V42" s="9" t="n">
-        <v>0</v>
+      <c r="V42" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X42" s="9" t="n">
-        <v>1</v>
+      <c r="X42" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y42" s="9" t="n">
         <v>0</v>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5057,13 +5057,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
@@ -5104,8 +5104,8 @@
       <c r="V43" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W43" s="9" t="n">
-        <v>3</v>
+      <c r="W43" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X43" s="10" t="n">
         <v>7</v>
@@ -5162,17 +5162,17 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M44" s="8" t="n">
@@ -5263,13 +5263,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5364,13 +5364,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>4</v>
       </c>
       <c r="W46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X46" s="10" t="n">
         <v>7</v>
@@ -5465,13 +5465,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>1</v>
       </c>
       <c r="V47" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
@@ -5570,13 +5570,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-8</v>
+        <v>-22</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5671,13 +5671,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>0</v>
       </c>
       <c r="X51" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y51" s="9" t="n">
         <v>0</v>
@@ -6079,17 +6079,17 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M53" s="8" t="n">
@@ -6184,13 +6184,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -6285,13 +6285,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6330,13 +6330,13 @@
         <v>0</v>
       </c>
       <c r="V55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X55" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y55" s="9" t="n">
         <v>0</v>
@@ -6386,13 +6386,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6487,13 +6487,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6588,17 +6588,17 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M58" s="8" t="n">
@@ -6632,8 +6632,8 @@
       <c r="U58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V58" s="9" t="n">
-        <v>0</v>
+      <c r="V58" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6693,13 +6693,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>4</v>
       </c>
       <c r="W59" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X59" s="10" t="n">
         <v>5</v>
@@ -6798,17 +6798,17 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M60" s="8" t="n">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6899,13 +6899,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -6943,11 +6943,11 @@
       <c r="U61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V61" s="9" t="n">
-        <v>0</v>
+      <c r="V61" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W61" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X61" s="10" t="n">
         <v>7</v>
@@ -7004,13 +7004,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -7109,13 +7109,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="Q63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63" s="9" t="n">
         <v>0</v>
@@ -7214,13 +7214,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -7319,17 +7319,17 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M65" s="8" t="n">
@@ -7410,7 +7410,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
@@ -7453,8 +7453,8 @@
       <c r="P66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" s="9" t="n">
-        <v>1</v>
+      <c r="Q66" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R66" s="9" t="n">
         <v>0</v>
@@ -7469,7 +7469,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7529,13 +7529,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7675,11 +7675,11 @@
       <c r="T68" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U68" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" s="9" t="n">
-        <v>2</v>
+      <c r="U68" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V68" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7739,13 +7739,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
@@ -7844,13 +7844,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7945,13 +7945,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8046,17 +8046,17 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>11</v>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M72" s="8" t="n">
@@ -8090,11 +8090,11 @@
       <c r="U72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W72" s="9" t="n">
-        <v>0</v>
+      <c r="V72" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W72" s="10" t="n">
+        <v>13</v>
       </c>
       <c r="X72" s="10" t="n">
         <v>7</v>
@@ -8147,13 +8147,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -8252,17 +8252,17 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L74" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M74" s="8" t="n">
@@ -8458,13 +8458,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>4</v>
       </c>
       <c r="W76" s="10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X76" s="10" t="n">
         <v>7</v>
@@ -8664,13 +8664,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8866,13 +8866,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8893,10 +8893,10 @@
         </is>
       </c>
       <c r="P80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q80" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R80" s="9" t="n">
         <v>0</v>
@@ -8913,8 +8913,8 @@
       <c r="V80" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W80" s="9" t="n">
-        <v>3</v>
+      <c r="W80" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X80" s="10" t="n">
         <v>5</v>
@@ -8967,13 +8967,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q81" s="9" t="n">
         <v>0</v>
@@ -9068,17 +9068,17 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L82" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M82" s="8" t="n">
@@ -9095,7 +9095,7 @@
         </is>
       </c>
       <c r="P82" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q82" s="9" t="n">
         <v>0</v>
@@ -9116,7 +9116,7 @@
         <v>4</v>
       </c>
       <c r="W82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X82" s="10" t="n">
         <v>7</v>
@@ -9173,13 +9173,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>2</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9375,13 +9375,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9480,17 +9480,17 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L86" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M86" s="8" t="n">
@@ -9518,8 +9518,8 @@
       <c r="S86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T86" s="9" t="n">
-        <v>0</v>
+      <c r="T86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U86" s="9" t="n">
         <v>0</v>
@@ -9585,13 +9585,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>1</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9690,13 +9690,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>0</v>
       </c>
       <c r="S88" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T88" s="10" t="n">
         <v>1</v>
@@ -9795,13 +9795,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9896,13 +9896,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9997,13 +9997,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>4</v>
       </c>
       <c r="W91" s="10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X91" s="10" t="n">
         <v>7</v>
@@ -10102,13 +10102,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>9</v>
+        <v>-2</v>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>4</v>
       </c>
       <c r="W92" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X92" s="10" t="n">
         <v>4</v>
@@ -10207,17 +10207,17 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="L93" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M93" s="8" t="n">
@@ -10308,13 +10308,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
@@ -10413,13 +10413,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -10619,13 +10619,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>4</v>
       </c>
       <c r="W97" s="10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X97" s="10" t="n">
         <v>7</v>
@@ -10805,7 +10805,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10819,13 +10819,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10848,8 +10848,8 @@
       <c r="P99" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="Q99" s="9" t="n">
-        <v>1</v>
+      <c r="Q99" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R99" s="9" t="n">
         <v>0</v>
@@ -10924,17 +10924,17 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>4</v>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M100" s="8" t="n">
@@ -11015,7 +11015,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11029,13 +11029,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
@@ -11070,14 +11070,14 @@
       <c r="T101" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U101" s="9" t="n">
-        <v>0</v>
+      <c r="U101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V101" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W101" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X101" s="10" t="n">
         <v>7</v>
@@ -11116,7 +11116,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -11130,17 +11130,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>29</v>
+      </c>
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M102" s="8" t="n">
@@ -11174,11 +11174,11 @@
       <c r="U102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W102" s="9" t="n">
-        <v>0</v>
+      <c r="V102" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W102" s="10" t="n">
+        <v>25</v>
       </c>
       <c r="X102" s="10" t="n">
         <v>7</v>
@@ -11217,7 +11217,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11231,17 +11231,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L103" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M103" s="8" t="n">
@@ -11275,8 +11275,8 @@
       <c r="U103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V103" s="9" t="n">
-        <v>2</v>
+      <c r="V103" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
@@ -11322,7 +11322,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11336,13 +11336,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
@@ -11380,11 +11380,11 @@
       <c r="U104" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="V104" s="9" t="n">
-        <v>3</v>
+      <c r="V104" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W104" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X104" s="10" t="n">
         <v>7</v>
@@ -11441,13 +11441,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>0</v>
       </c>
       <c r="S105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T105" s="10" t="n">
         <v>1</v>
@@ -11542,13 +11542,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11643,17 +11643,17 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L107" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M107" s="8" t="n">
@@ -11691,7 +11691,7 @@
         <v>4</v>
       </c>
       <c r="W107" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X107" s="10" t="n">
         <v>7</v>
@@ -11744,13 +11744,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>9</v>
+        <v>-3</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>2</v>
       </c>
       <c r="R108" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S108" s="10" t="n">
         <v>2</v>
@@ -11786,13 +11786,13 @@
         <v>1</v>
       </c>
       <c r="U108" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V108" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W108" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>7</v>
@@ -11835,7 +11835,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11849,13 +11849,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11893,8 +11893,8 @@
       <c r="U109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V109" s="9" t="n">
-        <v>1</v>
+      <c r="V109" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -11950,13 +11950,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -12049,17 +12049,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M111" s="8" t="n">
@@ -12094,7 +12094,7 @@
         <v>0</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -12148,13 +12148,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12247,13 +12247,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q113" s="9" t="n">
         <v>0</v>
@@ -12291,8 +12291,8 @@
       <c r="U113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V113" s="9" t="n">
-        <v>2</v>
+      <c r="V113" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -12346,13 +12346,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>1</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
@@ -12431,7 +12431,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12445,13 +12445,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>0</v>
       </c>
       <c r="Q115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R115" s="9" t="n">
         <v>0</v>
@@ -12489,8 +12489,8 @@
       <c r="U115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V115" s="9" t="n">
-        <v>2</v>
+      <c r="V115" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -12544,13 +12544,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
@@ -12643,13 +12643,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
@@ -12691,7 +12691,7 @@
         <v>4</v>
       </c>
       <c r="W117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X117" s="10" t="n">
         <v>4</v>
@@ -12742,17 +12742,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-24</v>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12787,7 +12787,7 @@
         <v>0</v>
       </c>
       <c r="V118" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
@@ -12827,7 +12827,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12841,17 +12841,17 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L119" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L119" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M119" s="8" t="n">
@@ -12871,7 +12871,7 @@
         <v>3</v>
       </c>
       <c r="Q119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R119" s="9" t="n">
         <v>0</v>
@@ -12888,8 +12888,8 @@
       <c r="V119" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W119" s="9" t="n">
-        <v>1</v>
+      <c r="W119" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X119" s="10" t="n">
         <v>7</v>
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13039,17 +13039,17 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L121" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L121" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M121" s="8" t="n">
@@ -13068,8 +13068,8 @@
       <c r="P121" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="Q121" s="9" t="n">
-        <v>1</v>
+      <c r="Q121" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R121" s="9" t="n">
         <v>0</v>
@@ -13086,8 +13086,8 @@
       <c r="V121" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W121" s="9" t="n">
-        <v>2</v>
+      <c r="W121" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X121" s="10" t="n">
         <v>7</v>
@@ -13138,13 +13138,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         </is>
       </c>
       <c r="P122" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q122" s="10" t="n">
         <v>2</v>
@@ -13183,7 +13183,7 @@
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -13357,13 +13357,13 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -13372,7 +13372,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -13405,7 +13405,7 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -13489,7 +13489,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -13504,7 +13504,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -13522,7 +13522,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -13537,7 +13537,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -13555,7 +13555,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -13570,7 +13570,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -13636,7 +13636,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -13654,7 +13654,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13669,7 +13669,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13687,7 +13687,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13702,7 +13702,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -13720,7 +13720,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13735,7 +13735,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -13753,13 +13753,13 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -13786,7 +13786,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13852,13 +13852,13 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -13867,7 +13867,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -13885,7 +13885,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13900,7 +13900,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -13966,7 +13966,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -13984,14 +13984,14 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
         <v>2</v>
       </c>
-      <c r="F23" t="n">
-        <v>3</v>
-      </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
@@ -13999,7 +13999,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -14017,13 +14017,13 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -14050,7 +14050,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -14065,7 +14065,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -14083,7 +14083,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -14098,7 +14098,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -14116,7 +14116,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -14149,13 +14149,13 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -14164,7 +14164,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/20/inyear.xlsx
+++ b/docs/d/20/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/20/inyear.xlsx
+++ b/docs/d/20/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/20/inyear.xlsx
+++ b/docs/d/20/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/20/inyear.xlsx
+++ b/docs/d/20/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/20/inyear.xlsx
+++ b/docs/d/20/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 14 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 14 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 35 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 35 clubs short</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         <v>2</v>
       </c>
       <c r="R3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" s="9" t="n">
         <v>1</v>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -2506,13 +2506,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-23</v>
+        <v>-15</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="P19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="9" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3465,8 +3465,8 @@
       <c r="S27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T27" s="9" t="n">
-        <v>0</v>
+      <c r="T27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U27" s="9" t="n">
         <v>0</v>
@@ -4237,13 +4237,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>0</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" s="9" t="n">
         <v>0</v>
@@ -4681,7 +4681,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T39" s="9" t="n">
         <v>0</v>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="P43" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q43" s="9" t="n">
         <v>0</v>
@@ -5263,13 +5263,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         </is>
       </c>
       <c r="P53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" s="9" t="n">
         <v>0</v>
@@ -6285,13 +6285,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6588,17 +6588,17 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L58" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M58" s="8" t="n">
@@ -6636,7 +6636,7 @@
         <v>4</v>
       </c>
       <c r="W58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X58" s="10" t="n">
         <v>7</v>
@@ -6693,13 +6693,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>4</v>
       </c>
       <c r="W59" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X59" s="10" t="n">
         <v>5</v>
@@ -7346,7 +7346,7 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q65" s="9" t="n">
         <v>0</v>
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7766,7 +7766,7 @@
         </is>
       </c>
       <c r="P69" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q69" s="9" t="n">
         <v>0</v>
@@ -7777,8 +7777,8 @@
       <c r="S69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T69" s="9" t="n">
-        <v>0</v>
+      <c r="T69" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U69" s="9" t="n">
         <v>0</v>
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7882,8 +7882,8 @@
       <c r="S70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T70" s="9" t="n">
-        <v>0</v>
+      <c r="T70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U70" s="9" t="n">
         <v>0</v>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7945,17 +7945,17 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L71" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>12</v>
+      </c>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M71" s="8" t="n">
@@ -7989,11 +7989,11 @@
       <c r="U71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W71" s="9" t="n">
-        <v>0</v>
+      <c r="V71" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W71" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="X71" s="10" t="n">
         <v>7</v>
@@ -9068,17 +9068,17 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L82" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M82" s="8" t="n">
@@ -9110,13 +9110,13 @@
         <v>1</v>
       </c>
       <c r="U82" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V82" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W82" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X82" s="10" t="n">
         <v>7</v>
@@ -9585,13 +9585,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9690,13 +9690,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9719,8 +9719,8 @@
       <c r="P88" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q88" s="9" t="n">
-        <v>1</v>
+      <c r="Q88" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R88" s="9" t="n">
         <v>0</v>
@@ -9738,7 +9738,7 @@
         <v>4</v>
       </c>
       <c r="W88" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X88" s="10" t="n">
         <v>7</v>
@@ -9795,13 +9795,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -10138,7 +10138,7 @@
         <v>2</v>
       </c>
       <c r="S92" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T92" s="10" t="n">
         <v>1</v>
@@ -10344,7 +10344,7 @@
         <v>2</v>
       </c>
       <c r="S94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T94" s="10" t="n">
         <v>1</v>
@@ -10619,13 +10619,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>4</v>
       </c>
       <c r="W97" s="10" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="X97" s="10" t="n">
         <v>7</v>
@@ -11231,13 +11231,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         </is>
       </c>
       <c r="P103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q103" s="9" t="n">
         <v>0</v>
@@ -11542,13 +11542,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
@@ -11670,7 +11670,7 @@
         </is>
       </c>
       <c r="P107" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q107" s="9" t="n">
         <v>1</v>
@@ -11744,13 +11744,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>2</v>
       </c>
       <c r="R108" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S108" s="10" t="n">
         <v>2</v>
@@ -12049,13 +12049,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>0</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -12277,7 +12277,7 @@
         <v>1</v>
       </c>
       <c r="Q113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>0</v>
@@ -12728,7 +12728,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12742,17 +12742,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-24</v>
-      </c>
-      <c r="L118" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-20</v>
+      </c>
+      <c r="L118" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12786,11 +12786,11 @@
       <c r="U118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V118" s="9" t="n">
-        <v>3</v>
+      <c r="V118" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X118" s="10" t="n">
         <v>7</v>
@@ -13072,7 +13072,7 @@
         <v>2</v>
       </c>
       <c r="R121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S121" s="9" t="n">
         <v>0</v>
@@ -13456,7 +13456,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -13669,7 +13669,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -13753,7 +13753,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -13786,7 +13786,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13801,7 +13801,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -13867,7 +13867,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -13918,7 +13918,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="E21" t="n">
         <v>2</v>
@@ -14149,7 +14149,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -14164,7 +14164,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/20/inyear.xlsx
+++ b/docs/d/20/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$123</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 14 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 14 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 35 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 35 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC122"/>
+  <dimension ref="A1:AC123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1914,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="9" t="n">
         <v>0</v>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Senthamil Solvendhar Peravai</t>
+          <t>Senthamil Slovendar Peravai</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
@@ -3835,13 +3835,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>1</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" s="9" t="n">
         <v>0</v>
@@ -5290,7 +5290,7 @@
         </is>
       </c>
       <c r="P45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q45" s="9" t="n">
         <v>1</v>
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6937,8 +6937,8 @@
       <c r="S61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T61" s="9" t="n">
-        <v>0</v>
+      <c r="T61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U61" s="9" t="n">
         <v>0</v>
@@ -7319,13 +7319,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -8801,7 +8801,7 @@
         <v>0</v>
       </c>
       <c r="S79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T79" s="10" t="n">
         <v>1</v>
@@ -8866,13 +8866,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9585,13 +9585,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9629,8 +9629,8 @@
       <c r="U87" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V87" s="9" t="n">
-        <v>3</v>
+      <c r="V87" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9795,13 +9795,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         </is>
       </c>
       <c r="P92" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q92" s="10" t="n">
         <v>2</v>
@@ -10207,17 +10207,17 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L93" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>44</v>
+      </c>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M93" s="8" t="n">
@@ -10255,7 +10255,7 @@
         <v>4</v>
       </c>
       <c r="W93" s="10" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="X93" s="10" t="n">
         <v>7</v>
@@ -10619,13 +10619,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>2</v>
       </c>
       <c r="Q97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R97" s="9" t="n">
         <v>0</v>
@@ -10667,7 +10667,7 @@
         <v>4</v>
       </c>
       <c r="W97" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X97" s="10" t="n">
         <v>7</v>
@@ -10720,13 +10720,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>4</v>
       </c>
       <c r="W98" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X98" s="10" t="n">
         <v>7</v>
@@ -10852,10 +10852,10 @@
         <v>2</v>
       </c>
       <c r="R99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T99" s="10" t="n">
         <v>1</v>
@@ -11209,15 +11209,15 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>7980</v>
+        <v>28681028</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KOTC Toastmasters Club</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11231,17 +11231,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L103" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L103" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M103" s="8" t="n">
@@ -11258,7 +11258,7 @@
         </is>
       </c>
       <c r="P103" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q103" s="9" t="n">
         <v>0</v>
@@ -11267,7 +11267,7 @@
         <v>0</v>
       </c>
       <c r="S103" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T103" s="9" t="n">
         <v>0</v>
@@ -11275,14 +11275,14 @@
       <c r="U103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V103" s="10" t="n">
-        <v>4</v>
+      <c r="V103" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X103" s="10" t="n">
-        <v>4</v>
+      <c r="X103" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y103" s="9" t="n">
         <v>0</v>
@@ -11293,14 +11293,8 @@
       <c r="AA103" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB103" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC103" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AB103" s="4" t="n"/>
+      <c r="AC103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -11314,15 +11308,15 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>3625652</v>
+        <v>7980</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Life Principles</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11336,17 +11330,17 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L104" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M104" s="8" t="n">
@@ -11366,28 +11360,28 @@
         <v>1</v>
       </c>
       <c r="Q104" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S104" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T104" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U104" s="10" t="n">
-        <v>4</v>
+      <c r="S104" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V104" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W104" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X104" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y104" s="9" t="n">
         <v>0</v>
@@ -11403,7 +11397,7 @@
       </c>
       <c r="AC104" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -11419,15 +11413,15 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>996235</v>
+        <v>3625652</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Pearl of the Gulf</t>
+          <t>Life Principles</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11441,17 +11435,17 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L105" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M105" s="8" t="n">
@@ -11471,25 +11465,25 @@
         <v>1</v>
       </c>
       <c r="Q105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S105" s="9" t="n">
-        <v>1</v>
+      <c r="S105" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T105" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V105" s="9" t="n">
-        <v>1</v>
+      <c r="U105" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V105" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W105" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X105" s="10" t="n">
         <v>7</v>
@@ -11504,9 +11498,13 @@
         <v>1</v>
       </c>
       <c r="AB105" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC105" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC105" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -11516,19 +11514,19 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>5940312</v>
+        <v>996235</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Mangaf Communicators</t>
+          <t>Pearl of the Gulf</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11542,13 +11540,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11569,19 +11567,19 @@
         </is>
       </c>
       <c r="P106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q106" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U106" s="9" t="n">
         <v>0</v>
@@ -11593,13 +11591,13 @@
         <v>0</v>
       </c>
       <c r="X106" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="9" t="n">
-        <v>0</v>
+      <c r="Z106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
@@ -11621,15 +11619,15 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>7800623</v>
+        <v>5940312</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Nebras Toastmasters Club</t>
+          <t>Mangaf Communicators</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11643,13 +11641,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11670,7 +11668,7 @@
         </is>
       </c>
       <c r="P107" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q107" s="9" t="n">
         <v>1</v>
@@ -11687,26 +11685,26 @@
       <c r="U107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V107" s="10" t="n">
+      <c r="V107" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W107" s="10" t="n">
+      <c r="Y107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA107" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB107" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="X107" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z107" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA107" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB107" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="AC107" s="4" t="inlineStr"/>
     </row>
@@ -11722,15 +11720,15 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>3041786</v>
+        <v>7800623</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Rawasi</t>
+          <t>Nebras Toastmasters Club</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11744,17 +11742,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M108" s="8" t="n">
@@ -11770,29 +11768,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P108" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q108" s="10" t="n">
+      <c r="P108" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R108" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="S108" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T108" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U108" s="10" t="n">
-        <v>2</v>
+      <c r="Q108" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V108" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W108" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>7</v>
@@ -11807,13 +11805,9 @@
         <v>1</v>
       </c>
       <c r="AB108" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC108" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC108" s="4" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -11827,15 +11821,15 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>951706</v>
+        <v>3041786</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>South Kuwait Toastmasters Club</t>
+          <t>Rawasi</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11849,17 +11843,17 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L109" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L109" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M109" s="8" t="n">
@@ -11875,29 +11869,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S109" s="9" t="n">
-        <v>0</v>
+      <c r="P109" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q109" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R109" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S109" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T109" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U109" s="9" t="n">
-        <v>0</v>
+      <c r="U109" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V109" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W109" s="9" t="n">
-        <v>0</v>
+      <c r="W109" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X109" s="10" t="n">
         <v>7</v>
@@ -11912,31 +11906,35 @@
         <v>1</v>
       </c>
       <c r="AB109" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC109" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC109" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>6386</v>
+        <v>951706</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Moscow Free Speakers Club</t>
+          <t>South Kuwait Toastmasters Club</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11950,13 +11948,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -11994,14 +11992,14 @@
       <c r="U110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V110" s="9" t="n">
-        <v>1</v>
+      <c r="V110" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X110" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y110" s="9" t="n">
         <v>0</v>
@@ -12012,7 +12010,9 @@
       <c r="AA110" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB110" s="4" t="n"/>
+      <c r="AB110" s="4" t="n">
+        <v>7</v>
+      </c>
       <c r="AC110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
@@ -12027,15 +12027,15 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>2539011</v>
+        <v>6386</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Moscow Toastbusters</t>
+          <t>Moscow Free Speakers Club</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12049,13 +12049,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q111" s="9" t="n">
         <v>0</v>
@@ -12087,14 +12087,14 @@
       <c r="S111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T111" s="9" t="n">
-        <v>0</v>
+      <c r="T111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -12126,11 +12126,11 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>4399476</v>
+        <v>2539011</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Saint Petersburg Toastmasters</t>
+          <t>Moscow Toastbusters</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
@@ -12148,13 +12148,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>0</v>
       </c>
       <c r="S112" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T112" s="9" t="n">
         <v>0</v>
@@ -12199,7 +12199,7 @@
         <v>0</v>
       </c>
       <c r="X112" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y112" s="9" t="n">
         <v>0</v>
@@ -12225,35 +12225,35 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>3785969</v>
+        <v>4399476</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>WorldSurfers</t>
+          <t>Saint Petersburg Toastmasters</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G113" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I113" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="J113" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K113" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F113" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G113" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H113" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I113" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="J113" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="K113" s="4" t="n">
-        <v>-2</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12277,13 +12277,13 @@
         <v>1</v>
       </c>
       <c r="Q113" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T113" s="9" t="n">
         <v>0</v>
@@ -12291,8 +12291,8 @@
       <c r="U113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V113" s="10" t="n">
-        <v>4</v>
+      <c r="V113" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -12320,19 +12320,19 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>5246376</v>
+        <v>3785969</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Autour Du Mot</t>
+          <t>WorldSurfers</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12346,13 +12346,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>1</v>
       </c>
       <c r="Q114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R114" s="9" t="n">
         <v>0</v>
@@ -12384,14 +12384,14 @@
       <c r="S114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T114" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U114" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V114" s="9" t="n">
-        <v>1</v>
+      <c r="T114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
@@ -12423,15 +12423,15 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>6890761</v>
+        <v>5246376</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Optima Forma</t>
+          <t>Autour Du Mot</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12445,13 +12445,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -12472,10 +12472,10 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q115" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R115" s="9" t="n">
         <v>0</v>
@@ -12483,14 +12483,14 @@
       <c r="S115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T115" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U115" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V115" s="10" t="n">
-        <v>4</v>
+      <c r="T115" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U115" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V115" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -12522,15 +12522,15 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>606654</v>
+        <v>6890761</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Redefluss Moskau Club</t>
+          <t>Optima Forma</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12547,10 +12547,10 @@
         <v>9</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12574,13 +12574,13 @@
         <v>0</v>
       </c>
       <c r="Q116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S116" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T116" s="9" t="n">
         <v>0</v>
@@ -12588,20 +12588,20 @@
       <c r="U116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V116" s="9" t="n">
-        <v>2</v>
+      <c r="V116" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X116" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -12621,15 +12621,15 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>6082035</v>
+        <v>606654</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Zlatoust Masters</t>
+          <t>Redefluss Moskau Club</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12643,17 +12643,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L117" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L117" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M117" s="8" t="n">
@@ -12670,7 +12670,7 @@
         </is>
       </c>
       <c r="P117" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q117" s="9" t="n">
         <v>0</v>
@@ -12679,7 +12679,7 @@
         <v>0</v>
       </c>
       <c r="S117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T117" s="9" t="n">
         <v>0</v>
@@ -12687,11 +12687,11 @@
       <c r="U117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V117" s="10" t="n">
-        <v>4</v>
+      <c r="V117" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W117" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X117" s="10" t="n">
         <v>4</v>
@@ -12699,8 +12699,8 @@
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="10" t="n">
-        <v>1</v>
+      <c r="Z117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
@@ -12716,15 +12716,15 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>2686258</v>
+        <v>6082035</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Almaty Toastmasters</t>
+          <t>Zlatoust Masters</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
@@ -12745,10 +12745,10 @@
         <v>20</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-20</v>
+        <v>2</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -12769,10 +12769,10 @@
         </is>
       </c>
       <c r="P118" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R118" s="9" t="n">
         <v>0</v>
@@ -12793,7 +12793,7 @@
         <v>1</v>
       </c>
       <c r="X118" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
@@ -12819,15 +12819,15 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>1338915</v>
+        <v>2686258</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Astana Toastmasters Club</t>
+          <t>Almaty Toastmasters</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12841,17 +12841,17 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L119" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-21</v>
+      </c>
+      <c r="L119" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M119" s="8" t="n">
@@ -12879,8 +12879,8 @@
       <c r="S119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T119" s="10" t="n">
-        <v>1</v>
+      <c r="T119" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U119" s="9" t="n">
         <v>0</v>
@@ -12888,8 +12888,8 @@
       <c r="V119" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W119" s="10" t="n">
-        <v>7</v>
+      <c r="W119" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="X119" s="10" t="n">
         <v>7</v>
@@ -12918,15 +12918,15 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>6011675</v>
+        <v>1338915</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Atyrau Open Toastmasters</t>
+          <t>Astana Toastmasters Club</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12940,13 +12940,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -12954,11 +12954,11 @@
         </is>
       </c>
       <c r="M120" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N120" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O120" s="7" t="inlineStr">
@@ -12966,11 +12966,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P120" s="9" t="n">
-        <v>0</v>
+      <c r="P120" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R120" s="9" t="n">
         <v>0</v>
@@ -12978,29 +12978,29 @@
       <c r="S120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T120" s="9" t="n">
-        <v>0</v>
+      <c r="T120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V120" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W120" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X120" s="9" t="n">
-        <v>0</v>
+      <c r="V120" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W120" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="X120" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA120" s="9" t="n">
-        <v>0</v>
+      <c r="Z120" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB120" s="4" t="n"/>
       <c r="AC120" s="4" t="inlineStr"/>
@@ -13017,15 +13017,15 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>28678115</v>
+        <v>6011675</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Qazaq Toastmasters</t>
+          <t>Atyrau Open Toastmasters</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13039,13 +13039,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -13053,11 +13053,11 @@
         </is>
       </c>
       <c r="M121" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N121" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O121" s="7" t="inlineStr">
@@ -13065,41 +13065,41 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P121" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q121" s="10" t="n">
-        <v>2</v>
+      <c r="P121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R121" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T121" s="10" t="n">
-        <v>1</v>
+      <c r="T121" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V121" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W121" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="X121" s="10" t="n">
-        <v>7</v>
+      <c r="V121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X121" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z121" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA121" s="10" t="n">
-        <v>1</v>
+      <c r="Z121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA121" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB121" s="4" t="n"/>
       <c r="AC121" s="4" t="inlineStr"/>
@@ -13116,15 +13116,15 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>28677857</v>
+        <v>28678115</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Zhetysu Toastmasters</t>
+          <t>Qazaq Toastmasters</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13138,10 +13138,10 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K122" s="4" t="n">
         <v>-3</v>
@@ -13164,32 +13164,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P122" s="9" t="n">
-        <v>2</v>
+      <c r="P122" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Q122" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V122" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W122" s="9" t="n">
-        <v>0</v>
+      <c r="V122" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W122" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X122" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y122" s="9" t="n">
         <v>0</v>
@@ -13203,8 +13203,107 @@
       <c r="AB122" s="4" t="n"/>
       <c r="AC122" s="4" t="inlineStr"/>
     </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="n">
+        <v>28677857</v>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>Zhetysu Toastmasters</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F123" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G123" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J123" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K123" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L123" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M123" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N123" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O123" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P123" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q123" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R123" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X123" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z123" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA123" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB123" s="4" t="n"/>
+      <c r="AC123" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC122"/>
+  <autoFilter ref="A1:AC123"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13687,7 +13786,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13885,7 +13984,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13966,7 +14065,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -14014,25 +14113,25 @@
         </is>
       </c>
       <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
         <v>4</v>
       </c>
-      <c r="D24" t="n">
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>3</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="n">
-        <v>3</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -14149,13 +14248,13 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
